--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL/UR/UR_TIRMIDHI.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL/UR/UR_TIRMIDHI.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,47 +433,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>book_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>language_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>hadith_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ur</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>3121</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>[ { "id": "3121", "meta_data": { "title": "$book_name$ $hadith_number$ - پل صراط اور قیامت کا منظر | $publication$", "description": "Read $book_name$ $hadith_number$ from the $chapter_name$ chapter. قیامت کے دن زمین بدلنے پر لوگ پل صراط پر ہوں گے۔" }, "content": { "heading": "پل صراط کا حدیث: قیامت کے دن لوگ کہاں ہوں گے؟", "explanation": "یہ حدیث قیامت کے ایک بڑے منظر کو صاف الفاظ میں بیان کرتی ہے۔ ام المؤمنین عائشہ رضی الله عنہا نے قرآن کی آیت پڑھی جس میں بتایا گیا ہے کہ اس دن زمین اور آسمان بدل دیے جائیں گے۔ انہوں نے رسول اللہ صلی اللہ علیہ وسلم سے پوچھا کہ اس وقت لوگ کہاں ہوں گے؟ آپ صلی اللہ علیہ وسلم نے جواب دیا کہ وہ پل صراط پر ہوں گے۔ اس حدیث کا اصل موضوع پل صراط، قیامت کا دن، اور آخرت کی حقیقت ہے۔ یہ ہمیں یاد دلاتی ہے کہ قیامت صرف ایک عام دن نہیں ہوگا، بلکہ زمین و آسمان کی حالت بدل جائے گی۔ اس وقت انسان اپنی دنیاوی طاقت، مال، یا مقام کے بجائے اللہ کے فیصلے کے سامنے ہوگا۔ حدیث کا پیغام مختصر ہے، مگر بہت گہرا ہے: آخرت کی تیاری کو سنجیدگی سے لینا چاہیے۔", "teachings": [ "قیامت کے دن زمین اور آسمان کی حالت بدل دی جائے گی۔", "رسول اللہ صلی اللہ علیہ وسلم نے بتایا کہ اس وقت لوگ پل صراط پر ہوں گے۔", "آخرت کے سوالات صحابہ رضی اللہ عنہم سنجیدگی سے پوچھتے تھے۔", "یہ حدیث قیامت اور پل صراط پر ایمان کو یاد دلاتی ہے۔" ] }, "searching_terms": [ "پل صراط کی حدیث", "قیامت کے دن لوگ کہاں ہوں گے", "يوم تبدل الأرض غير الأرض حدیث", "hadith about sirat bridge", "Tirmidhi 3121 Urdu", "Aisha hadith about Day of Judgment", "قیامت کے دن زمین بدل دی جائے گی" ], "related_hadiths": [ "Sahih Muslim 2791a", "Sahih al-Bukhari 7439", "Sahih Muslim 183a (Related Narration)" ] } ]</t>
         </is>

--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL/UR/UR_TIRMIDHI.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL/UR/UR_TIRMIDHI.xlsx
@@ -60,8 +60,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
